--- a/reports/pdf_rolling5_20260921.xlsx
+++ b/reports/pdf_rolling5_20260921.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -562,14 +562,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-09-14 ~ 2026-09-21  (최근 5거래일)  ·  캡처 5/7  ·  대기: RISE, TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-09-14 ~ 2026-09-21  (최근 5거래일)  ·  캡처 4/7  ·  대기: PLUS, RISE, TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,609억   ·   현금 62억(1.3%)      오늘 2026-09-21  vs  5일전 2026-09-14      매수 12종목  /  매도 18종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,665억   ·   현금 31억(0.7%)      오늘 2026-09-21  vs  5일전 2026-09-14      매수 12종목  /  매도 18종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -665,7 +665,7 @@
         <v>150</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>3183181590</v>
+        <v>3173639618</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         <v>-130</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-892692246</v>
+        <v>-890016293</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>104</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>2857656227</v>
+        <v>2849090057</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>-101</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-911931476</v>
+        <v>-909197851</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>61</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>3260659029</v>
+        <v>3250884809</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>-80</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-3095093546</v>
+        <v>-3085815629</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>37</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1253703076</v>
+        <v>1249944950</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>-58</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1698197348</v>
+        <v>-1693106796</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>29</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>946345873</v>
+        <v>943509087</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>-49</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-3600198398</v>
+        <v>-3589406368</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>25</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>457457228</v>
+        <v>456085945</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>-39</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-1157506928</v>
+        <v>-1154037161</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>25</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>678177839</v>
+        <v>676144919</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>-33</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-2299097948</v>
+        <v>-2292206124</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>16</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1787386493</v>
+        <v>1782028586</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>-32</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-1793792896</v>
+        <v>-1788415785</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>969368884</v>
+        <v>966463084</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>-27</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-909459004</v>
+        <v>-906732791</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>7</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>2147646573</v>
+        <v>2141208743</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>-24</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-643843522</v>
+        <v>-641913523</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>7</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1305404752</v>
+        <v>1301491644</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>-16</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-300940790</v>
+        <v>-300038684</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>6</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>2723722360</v>
+        <v>2715557673</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>-16</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-528528264</v>
+        <v>-526943937</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>-12</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-455855628</v>
+        <v>-454489145</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>-11</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-905104652</v>
+        <v>-902391491</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>-9</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-1244143521</v>
+        <v>-1240414051</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1275,23 +1275,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-800299900</v>
+        <v>-1212569854</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>6.81%→6.54%</t>
+          <t>3.07%→2.51%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>195→190</t>
+          <t>53→48</t>
         </is>
       </c>
     </row>
@@ -1303,23 +1303,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-1216215608</v>
+        <v>-797900904</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>3.07%→2.51%</t>
+          <t>6.81%→6.54%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>53→48</t>
+          <t>195→190</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
         <v>-4</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-1311310655</v>
+        <v>-1307379843</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,398억   ·   현금 118억(3.5%)      오늘 2026-09-21  vs  5일전 2026-09-14      매수 0종목  /  매도 1종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,342억   ·   현금 59억(1.8%)      오늘 2026-09-21  vs  5일전 2026-09-14      매수 0종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
@@ -1455,7 +1455,7 @@
         <v>-28</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-1634270213</v>
+        <v>-1637395138</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
     <row r="30" ht="19" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,547억   ·   현금 84억(3.2%)      오늘 2026-09-21  vs  5일전 2026-09-14      매수 4종목  /  매도 7종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,563억   ·   현금 42억(1.6%)      오늘 2026-09-21  vs  5일전 2026-09-14      매수 4종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B30" s="4" t="n"/>
@@ -1567,7 +1567,7 @@
         <v>100</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>3696440108</v>
+        <v>3696438699</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>-133</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-1224531036</v>
+        <v>-1224530569</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>66</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>1006018230</v>
+        <v>1006017846</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>-59</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-1193056735</v>
+        <v>-1193056280</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>24</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>5016792147</v>
+        <v>5016790235</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>-40</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-3429096101</v>
+        <v>-3429094793</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>12</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>1308621638</v>
+        <v>1308621139</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>-38</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-1902234456</v>
+        <v>-1902233731</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1741,23 +1741,23 @@
       <c r="E37" s="17" t="n"/>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H37" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-1234147236</v>
+        <v>-2242415211</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>0.77%→0.43%</t>
+          <t>5.98%→4.95%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
         <is>
-          <t>30→14</t>
+          <t>105→89</t>
         </is>
       </c>
     </row>
@@ -1769,23 +1769,23 @@
       <c r="E38" s="17" t="n"/>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H38" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-2242416066</v>
+        <v>-1234146766</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>5.98%→4.95%</t>
+          <t>0.77%→0.43%</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
         <is>
-          <t>105→89</t>
+          <t>30→14</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1804,7 @@
         <v>-15</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-471603014</v>
+        <v>-471602834</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
     <row r="41" ht="19" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,962억   ·   현금 23억(1.2%)      오늘 2026-09-21  vs  5일전 2026-09-14      매수 4종목  /  매도 4종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,903억   ·   현금 11억(0.6%)      오늘 2026-09-21  vs  5일전 2026-09-14      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B41" s="4" t="n"/>
@@ -2083,457 +2083,75 @@
       </c>
     </row>
     <row r="49" ht="19" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 280억   ·   현금 3억(1.1%)      오늘 2026-09-21  vs  5일전 2026-09-14      매수 7종목  /  매도 7종목</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="n"/>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
-      <c r="F49" s="4" t="n"/>
-      <c r="G49" s="4" t="n"/>
-      <c r="H49" s="4" t="n"/>
-      <c r="I49" s="4" t="n"/>
-      <c r="J49" s="4" t="n"/>
-      <c r="K49" s="4" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="n"/>
-      <c r="C50" s="6" t="n"/>
-      <c r="D50" s="6" t="n"/>
-      <c r="E50" s="6" t="n"/>
-      <c r="G50" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H50" s="8" t="n"/>
-      <c r="I50" s="8" t="n"/>
-      <c r="J50" s="8" t="n"/>
-      <c r="K50" s="8" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C51" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D51" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E51" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G51" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H51" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I51" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J51" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K51" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="10" t="inlineStr">
-        <is>
-          <t>상신이디피</t>
-        </is>
-      </c>
-      <c r="B52" s="11" t="n">
-        <v>63</v>
-      </c>
-      <c r="C52" s="11" t="n">
-        <v>95035500</v>
-      </c>
-      <c r="D52" s="12" t="inlineStr">
-        <is>
-          <t>1.72%→2.07%</t>
-        </is>
-      </c>
-      <c r="E52" s="13" t="inlineStr">
-        <is>
-          <t>319→382</t>
-        </is>
-      </c>
-      <c r="G52" s="14" t="inlineStr">
-        <is>
-          <t>씨에스베어링</t>
-        </is>
-      </c>
-      <c r="H52" s="15" t="n">
-        <v>-106</v>
-      </c>
-      <c r="I52" s="15" t="n">
-        <v>-35616000</v>
-      </c>
-      <c r="J52" s="16" t="inlineStr">
-        <is>
-          <t>2.95%→2.83%</t>
-        </is>
-      </c>
-      <c r="K52" s="13" t="inlineStr">
-        <is>
-          <t>2,452→2,346</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>샘씨엔에스</t>
-        </is>
-      </c>
-      <c r="B53" s="11" t="n">
-        <v>53</v>
-      </c>
-      <c r="C53" s="11" t="n">
-        <v>62179600</v>
-      </c>
-      <c r="D53" s="12" t="inlineStr">
-        <is>
-          <t>0.57%→0.79%</t>
-        </is>
-      </c>
-      <c r="E53" s="13" t="inlineStr">
-        <is>
-          <t>135→188</t>
-        </is>
-      </c>
-      <c r="G53" s="14" t="inlineStr">
-        <is>
-          <t>더블유씨피</t>
-        </is>
-      </c>
-      <c r="H53" s="15" t="n">
-        <v>-42</v>
-      </c>
-      <c r="I53" s="15" t="n">
-        <v>-28518000</v>
-      </c>
-      <c r="J53" s="16" t="inlineStr">
-        <is>
-          <t>7.25%→7.16%</t>
-        </is>
-      </c>
-      <c r="K53" s="13" t="inlineStr">
-        <is>
-          <t>2,980→2,938</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="10" t="inlineStr">
-        <is>
-          <t>서진시스템</t>
-        </is>
-      </c>
-      <c r="B54" s="11" t="n">
-        <v>39</v>
-      </c>
-      <c r="C54" s="11" t="n">
-        <v>93502500</v>
-      </c>
-      <c r="D54" s="12" t="inlineStr">
-        <is>
-          <t>6.89%→7.24%</t>
-        </is>
-      </c>
-      <c r="E54" s="13" t="inlineStr">
-        <is>
-          <t>802→841</t>
-        </is>
-      </c>
-      <c r="G54" s="14" t="inlineStr">
-        <is>
-          <t>비나텍</t>
-        </is>
-      </c>
-      <c r="H54" s="15" t="n">
-        <v>-23</v>
-      </c>
-      <c r="I54" s="15" t="n">
-        <v>-124614000</v>
-      </c>
-      <c r="J54" s="16" t="inlineStr">
-        <is>
-          <t>1.86%→1.42%</t>
-        </is>
-      </c>
-      <c r="K54" s="13" t="inlineStr">
-        <is>
-          <t>96→73</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="10" t="inlineStr">
-        <is>
-          <t>인텍플러스</t>
-        </is>
-      </c>
-      <c r="B55" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="C55" s="11" t="n">
-        <v>57417500</v>
-      </c>
-      <c r="D55" s="12" t="inlineStr">
-        <is>
-          <t>3.88%→4.10%</t>
-        </is>
-      </c>
-      <c r="E55" s="13" t="inlineStr">
-        <is>
-          <t>321→338</t>
-        </is>
-      </c>
-      <c r="G55" s="14" t="inlineStr">
-        <is>
-          <t>피에스케이홀딩스</t>
-        </is>
-      </c>
-      <c r="H55" s="15" t="n">
-        <v>-22</v>
-      </c>
-      <c r="I55" s="15" t="n">
-        <v>-257026000</v>
-      </c>
-      <c r="J55" s="16" t="inlineStr">
-        <is>
-          <t>3.72%→2.81%</t>
-        </is>
-      </c>
-      <c r="K55" s="13" t="inlineStr">
-        <is>
-          <t>89→67</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="10" t="inlineStr">
-        <is>
-          <t>파두</t>
-        </is>
-      </c>
-      <c r="B56" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="C56" s="11" t="n">
-        <v>62328000</v>
-      </c>
-      <c r="D56" s="12" t="inlineStr">
-        <is>
-          <t>1.05%→1.28%</t>
-        </is>
-      </c>
-      <c r="E56" s="13" t="inlineStr">
-        <is>
-          <t>66→80</t>
-        </is>
-      </c>
-      <c r="G56" s="14" t="inlineStr">
-        <is>
-          <t>클래시스</t>
-        </is>
-      </c>
-      <c r="H56" s="15" t="n">
-        <v>-16</v>
-      </c>
-      <c r="I56" s="15" t="n">
-        <v>-35224000</v>
-      </c>
-      <c r="J56" s="16" t="inlineStr">
-        <is>
-          <t>0.26%→0.13%</t>
-        </is>
-      </c>
-      <c r="K56" s="13" t="inlineStr">
-        <is>
-          <t>33→17</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="10" t="inlineStr">
-        <is>
-          <t>오름테라퓨틱</t>
-        </is>
-      </c>
-      <c r="B57" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="C57" s="11" t="n">
-        <v>33642000</v>
-      </c>
-      <c r="D57" s="12" t="inlineStr">
-        <is>
-          <t>0.29%→0.42%</t>
-        </is>
-      </c>
-      <c r="E57" s="13" t="inlineStr">
-        <is>
-          <t>22→31</t>
-        </is>
-      </c>
-      <c r="G57" s="14" t="inlineStr">
-        <is>
-          <t>코미코</t>
-        </is>
-      </c>
-      <c r="H57" s="15" t="n">
-        <v>-15</v>
-      </c>
-      <c r="I57" s="15" t="n">
-        <v>-30660000</v>
-      </c>
-      <c r="J57" s="16" t="inlineStr">
-        <is>
-          <t>2.64%→2.54%</t>
-        </is>
-      </c>
-      <c r="K57" s="13" t="inlineStr">
-        <is>
-          <t>361→346</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="inlineStr">
-        <is>
-          <t>기가비스</t>
-        </is>
-      </c>
-      <c r="B58" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C58" s="11" t="n">
-        <v>35000000</v>
-      </c>
-      <c r="D58" s="12" t="inlineStr">
-        <is>
-          <t>1.05%→1.18%</t>
-        </is>
-      </c>
-      <c r="E58" s="13" t="inlineStr">
-        <is>
-          <t>42→47</t>
-        </is>
-      </c>
-      <c r="G58" s="14" t="inlineStr">
-        <is>
-          <t>씨어스</t>
-        </is>
-      </c>
-      <c r="H58" s="15" t="n">
-        <v>-6</v>
-      </c>
-      <c r="I58" s="15" t="n">
-        <v>-9912000</v>
-      </c>
-      <c r="J58" s="16" t="inlineStr">
-        <is>
-          <t>5.14%→5.12%</t>
-        </is>
-      </c>
-      <c r="K58" s="13" t="inlineStr">
-        <is>
-          <t>869→863</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="19" customHeight="1">
-      <c r="A60" s="18" t="inlineStr">
+      <c r="A49" s="18" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B49" s="19" t="n"/>
+      <c r="C49" s="19" t="n"/>
+      <c r="D49" s="19" t="n"/>
+      <c r="E49" s="19" t="n"/>
+      <c r="F49" s="19" t="n"/>
+      <c r="G49" s="19" t="n"/>
+      <c r="H49" s="19" t="n"/>
+      <c r="I49" s="19" t="n"/>
+      <c r="J49" s="19" t="n"/>
+      <c r="K49" s="19" t="n"/>
+    </row>
+    <row r="51" ht="19" customHeight="1">
+      <c r="A51" s="18" t="inlineStr">
         <is>
           <t>■ RISE 바이오TOP10액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B60" s="19" t="n"/>
-      <c r="C60" s="19" t="n"/>
-      <c r="D60" s="19" t="n"/>
-      <c r="E60" s="19" t="n"/>
-      <c r="F60" s="19" t="n"/>
-      <c r="G60" s="19" t="n"/>
-      <c r="H60" s="19" t="n"/>
-      <c r="I60" s="19" t="n"/>
-      <c r="J60" s="19" t="n"/>
-      <c r="K60" s="19" t="n"/>
-    </row>
-    <row r="62" ht="19" customHeight="1">
-      <c r="A62" s="18" t="inlineStr">
+      <c r="B51" s="19" t="n"/>
+      <c r="C51" s="19" t="n"/>
+      <c r="D51" s="19" t="n"/>
+      <c r="E51" s="19" t="n"/>
+      <c r="F51" s="19" t="n"/>
+      <c r="G51" s="19" t="n"/>
+      <c r="H51" s="19" t="n"/>
+      <c r="I51" s="19" t="n"/>
+      <c r="J51" s="19" t="n"/>
+      <c r="K51" s="19" t="n"/>
+    </row>
+    <row r="53" ht="19" customHeight="1">
+      <c r="A53" s="18" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B62" s="19" t="n"/>
-      <c r="C62" s="19" t="n"/>
-      <c r="D62" s="19" t="n"/>
-      <c r="E62" s="19" t="n"/>
-      <c r="F62" s="19" t="n"/>
-      <c r="G62" s="19" t="n"/>
-      <c r="H62" s="19" t="n"/>
-      <c r="I62" s="19" t="n"/>
-      <c r="J62" s="19" t="n"/>
-      <c r="K62" s="19" t="n"/>
+      <c r="B53" s="19" t="n"/>
+      <c r="C53" s="19" t="n"/>
+      <c r="D53" s="19" t="n"/>
+      <c r="E53" s="19" t="n"/>
+      <c r="F53" s="19" t="n"/>
+      <c r="G53" s="19" t="n"/>
+      <c r="H53" s="19" t="n"/>
+      <c r="I53" s="19" t="n"/>
+      <c r="J53" s="19" t="n"/>
+      <c r="K53" s="19" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="17">
+    <mergeCell ref="G26:K26"/>
+    <mergeCell ref="A53:K53"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A3:K3"/>
     <mergeCell ref="A30:K30"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A2:K2"/>
     <mergeCell ref="G42:K42"/>
     <mergeCell ref="A49:K49"/>
-    <mergeCell ref="A60:K60"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A25:K25"/>
-    <mergeCell ref="A41:K41"/>
-    <mergeCell ref="A50:E50"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="G4:K4"/>
-    <mergeCell ref="G26:K26"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A62:K62"/>
-    <mergeCell ref="G50:K50"/>
+    <mergeCell ref="A51:K51"/>
     <mergeCell ref="A31:E31"/>
     <mergeCell ref="G31:K31"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="G4:K4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20260921.xlsx
+++ b/reports/pdf_rolling5_20260921.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-09-14 ~ 2026-09-21  (최근 5거래일)  ·  캡처 4/7  ·  대기: PLUS, RISE, TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-09-14 ~ 2026-09-21  (최근 5거래일)  ·  캡처 5/7  ·  대기: RISE, TIGER</t>
         </is>
       </c>
     </row>
@@ -1054,23 +1054,23 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>ISC</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>2141208743</v>
+        <v>1301491644</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>0.79%→1.19%</t>
+          <t>1.56%→1.77%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>11→18</t>
+          <t>37→44</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -1098,44 +1098,44 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>ISC</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1301491644</v>
+        <v>2141208743</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>1.56%→1.77%</t>
+          <t>0.79%→1.19%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>37→44</t>
+          <t>11→18</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>씨메스로보틱스</t>
+          <t>지투지바이오  (편출)</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-300038684</v>
+        <v>-526943937</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.23%→0.15%</t>
+          <t>0.12%→0.00%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>53→37</t>
+          <t>16→0</t>
         </is>
       </c>
     </row>
@@ -1163,23 +1163,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오  (편출)</t>
+          <t>씨메스로보틱스</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-526943937</v>
+        <v>-300038684</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.12%→0.00%</t>
+          <t>0.23%→0.15%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>16→0</t>
+          <t>53→37</t>
         </is>
       </c>
     </row>
@@ -1741,23 +1741,23 @@
       <c r="E37" s="17" t="n"/>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H37" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-2242415211</v>
+        <v>-1234146766</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>5.98%→4.95%</t>
+          <t>0.77%→0.43%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
         <is>
-          <t>105→89</t>
+          <t>30→14</t>
         </is>
       </c>
     </row>
@@ -1769,23 +1769,23 @@
       <c r="E38" s="17" t="n"/>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H38" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-1234146766</v>
+        <v>-2242415211</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>0.77%→0.43%</t>
+          <t>5.98%→4.95%</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
         <is>
-          <t>30→14</t>
+          <t>105→89</t>
         </is>
       </c>
     </row>
@@ -2083,75 +2083,457 @@
       </c>
     </row>
     <row r="49" ht="19" customHeight="1">
-      <c r="A49" s="18" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B49" s="19" t="n"/>
-      <c r="C49" s="19" t="n"/>
-      <c r="D49" s="19" t="n"/>
-      <c r="E49" s="19" t="n"/>
-      <c r="F49" s="19" t="n"/>
-      <c r="G49" s="19" t="n"/>
-      <c r="H49" s="19" t="n"/>
-      <c r="I49" s="19" t="n"/>
-      <c r="J49" s="19" t="n"/>
-      <c r="K49" s="19" t="n"/>
-    </row>
-    <row r="51" ht="19" customHeight="1">
-      <c r="A51" s="18" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 284억   ·   현금 2억(0.5%)      오늘 2026-09-21  vs  5일전 2026-09-14      매수 7종목  /  매도 7종목</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n"/>
+      <c r="C49" s="4" t="n"/>
+      <c r="D49" s="4" t="n"/>
+      <c r="E49" s="4" t="n"/>
+      <c r="F49" s="4" t="n"/>
+      <c r="G49" s="4" t="n"/>
+      <c r="H49" s="4" t="n"/>
+      <c r="I49" s="4" t="n"/>
+      <c r="J49" s="4" t="n"/>
+      <c r="K49" s="4" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n"/>
+      <c r="C50" s="6" t="n"/>
+      <c r="D50" s="6" t="n"/>
+      <c r="E50" s="6" t="n"/>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="n"/>
+      <c r="I50" s="8" t="n"/>
+      <c r="J50" s="8" t="n"/>
+      <c r="K50" s="8" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J51" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K51" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>상신이디피</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="n">
+        <v>63</v>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>101871058</v>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>1.82%→2.18%</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>319→382</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>씨에스베어링</t>
+        </is>
+      </c>
+      <c r="H52" s="15" t="n">
+        <v>-106</v>
+      </c>
+      <c r="I52" s="15" t="n">
+        <v>-33501319</v>
+      </c>
+      <c r="J52" s="16" t="inlineStr">
+        <is>
+          <t>2.73%→2.62%</t>
+        </is>
+      </c>
+      <c r="K52" s="13" t="inlineStr">
+        <is>
+          <t>2,452→2,346</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>샘씨엔에스</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="n">
+        <v>53</v>
+      </c>
+      <c r="C53" s="11" t="n">
+        <v>64257237</v>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>0.58%→0.81%</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <t>135→188</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>더블유씨피</t>
+        </is>
+      </c>
+      <c r="H53" s="15" t="n">
+        <v>-42</v>
+      </c>
+      <c r="I53" s="15" t="n">
+        <v>-30252617</v>
+      </c>
+      <c r="J53" s="16" t="inlineStr">
+        <is>
+          <t>7.57%→7.48%</t>
+        </is>
+      </c>
+      <c r="K53" s="13" t="inlineStr">
+        <is>
+          <t>2,980→2,938</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="n">
+        <v>39</v>
+      </c>
+      <c r="C54" s="11" t="n">
+        <v>92410553</v>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>6.70%→7.04%</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>802→841</t>
+        </is>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="H54" s="15" t="n">
+        <v>-23</v>
+      </c>
+      <c r="I54" s="15" t="n">
+        <v>-129927074</v>
+      </c>
+      <c r="J54" s="16" t="inlineStr">
+        <is>
+          <t>1.91%→1.46%</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="inlineStr">
+        <is>
+          <t>96→73</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="C55" s="11" t="n">
+        <v>55632532</v>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>3.70%→3.91%</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>321→338</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="n">
+        <v>-22</v>
+      </c>
+      <c r="I55" s="15" t="n">
+        <v>-246246141</v>
+      </c>
+      <c r="J55" s="16" t="inlineStr">
+        <is>
+          <t>3.51%→2.65%</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="inlineStr">
+        <is>
+          <t>89→67</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="C56" s="11" t="n">
+        <v>59780034</v>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>0.99%→1.21%</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>66→80</t>
+        </is>
+      </c>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>클래시스</t>
+        </is>
+      </c>
+      <c r="H56" s="15" t="n">
+        <v>-16</v>
+      </c>
+      <c r="I56" s="15" t="n">
+        <v>-35056020</v>
+      </c>
+      <c r="J56" s="16" t="inlineStr">
+        <is>
+          <t>0.25%→0.13%</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="inlineStr">
+        <is>
+          <t>33→17</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C57" s="11" t="n">
+        <v>23562013</v>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>0.20%→0.29%</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>22→31</t>
+        </is>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>코미코</t>
+        </is>
+      </c>
+      <c r="H57" s="15" t="n">
+        <v>-15</v>
+      </c>
+      <c r="I57" s="15" t="n">
+        <v>-32392519</v>
+      </c>
+      <c r="J57" s="16" t="inlineStr">
+        <is>
+          <t>2.75%→2.64%</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="inlineStr">
+        <is>
+          <t>361→346</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C58" s="11" t="n">
+        <v>39585023</v>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>1.17%→1.32%</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>42→47</t>
+        </is>
+      </c>
+      <c r="G58" s="14" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="H58" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I58" s="15" t="n">
+        <v>-10437006</v>
+      </c>
+      <c r="J58" s="16" t="inlineStr">
+        <is>
+          <t>5.33%→5.31%</t>
+        </is>
+      </c>
+      <c r="K58" s="13" t="inlineStr">
+        <is>
+          <t>869→863</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="19" customHeight="1">
+      <c r="A60" s="18" t="inlineStr">
         <is>
           <t>■ RISE 바이오TOP10액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B51" s="19" t="n"/>
-      <c r="C51" s="19" t="n"/>
-      <c r="D51" s="19" t="n"/>
-      <c r="E51" s="19" t="n"/>
-      <c r="F51" s="19" t="n"/>
-      <c r="G51" s="19" t="n"/>
-      <c r="H51" s="19" t="n"/>
-      <c r="I51" s="19" t="n"/>
-      <c r="J51" s="19" t="n"/>
-      <c r="K51" s="19" t="n"/>
-    </row>
-    <row r="53" ht="19" customHeight="1">
-      <c r="A53" s="18" t="inlineStr">
+      <c r="B60" s="19" t="n"/>
+      <c r="C60" s="19" t="n"/>
+      <c r="D60" s="19" t="n"/>
+      <c r="E60" s="19" t="n"/>
+      <c r="F60" s="19" t="n"/>
+      <c r="G60" s="19" t="n"/>
+      <c r="H60" s="19" t="n"/>
+      <c r="I60" s="19" t="n"/>
+      <c r="J60" s="19" t="n"/>
+      <c r="K60" s="19" t="n"/>
+    </row>
+    <row r="62" ht="19" customHeight="1">
+      <c r="A62" s="18" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B53" s="19" t="n"/>
-      <c r="C53" s="19" t="n"/>
-      <c r="D53" s="19" t="n"/>
-      <c r="E53" s="19" t="n"/>
-      <c r="F53" s="19" t="n"/>
-      <c r="G53" s="19" t="n"/>
-      <c r="H53" s="19" t="n"/>
-      <c r="I53" s="19" t="n"/>
-      <c r="J53" s="19" t="n"/>
-      <c r="K53" s="19" t="n"/>
+      <c r="B62" s="19" t="n"/>
+      <c r="C62" s="19" t="n"/>
+      <c r="D62" s="19" t="n"/>
+      <c r="E62" s="19" t="n"/>
+      <c r="F62" s="19" t="n"/>
+      <c r="G62" s="19" t="n"/>
+      <c r="H62" s="19" t="n"/>
+      <c r="I62" s="19" t="n"/>
+      <c r="J62" s="19" t="n"/>
+      <c r="K62" s="19" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="G26:K26"/>
-    <mergeCell ref="A53:K53"/>
-    <mergeCell ref="A4:E4"/>
+  <mergeCells count="19">
+    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="G42:K42"/>
+    <mergeCell ref="A49:K49"/>
+    <mergeCell ref="A60:K60"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A50:E50"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A30:K30"/>
     <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A25:K25"/>
-    <mergeCell ref="A41:K41"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="G42:K42"/>
-    <mergeCell ref="A49:K49"/>
-    <mergeCell ref="A51:K51"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="G26:K26"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A62:K62"/>
+    <mergeCell ref="G50:K50"/>
     <mergeCell ref="A31:E31"/>
     <mergeCell ref="G31:K31"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="G4:K4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20260921.xlsx
+++ b/reports/pdf_rolling5_20260921.xlsx
@@ -1054,23 +1054,23 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>ISC</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1301491644</v>
+        <v>2141208743</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>1.56%→1.77%</t>
+          <t>0.79%→1.19%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>37→44</t>
+          <t>11→18</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -1098,44 +1098,44 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>로보티즈</t>
+          <t>ISC</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>2141208743</v>
+        <v>1301491644</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>0.79%→1.19%</t>
+          <t>1.56%→1.77%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>11→18</t>
+          <t>37→44</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오  (편출)</t>
+          <t>씨메스로보틱스</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-526943937</v>
+        <v>-300038684</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.12%→0.00%</t>
+          <t>0.23%→0.15%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>16→0</t>
+          <t>53→37</t>
         </is>
       </c>
     </row>
@@ -1163,23 +1163,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>씨메스로보틱스</t>
+          <t>지투지바이오  (편출)</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-300038684</v>
+        <v>-526943937</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.23%→0.15%</t>
+          <t>0.12%→0.00%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>53→37</t>
+          <t>16→0</t>
         </is>
       </c>
     </row>
@@ -1275,23 +1275,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-1212569854</v>
+        <v>-797900904</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>3.07%→2.51%</t>
+          <t>6.81%→6.54%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>53→48</t>
+          <t>195→190</t>
         </is>
       </c>
     </row>
@@ -1303,23 +1303,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-797900904</v>
+        <v>-1212569854</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>6.81%→6.54%</t>
+          <t>3.07%→2.51%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>195→190</t>
+          <t>53→48</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260921.xlsx
+++ b/reports/pdf_rolling5_20260921.xlsx
@@ -1275,23 +1275,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-797900904</v>
+        <v>-1212569854</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>6.81%→6.54%</t>
+          <t>3.07%→2.51%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>195→190</t>
+          <t>53→48</t>
         </is>
       </c>
     </row>
@@ -1303,23 +1303,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-1212569854</v>
+        <v>-797900904</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>3.07%→2.51%</t>
+          <t>6.81%→6.54%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>53→48</t>
+          <t>195→190</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260921.xlsx
+++ b/reports/pdf_rolling5_20260921.xlsx
@@ -878,23 +878,23 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>에이프릴바이오  (신규)</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>25</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>456085945</v>
+        <v>676144919</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.10%</t>
+          <t>0.33%→0.47%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>0→25</t>
+          <t>56→81</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -922,23 +922,23 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>에이프릴바이오  (신규)</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>25</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>676144919</v>
+        <v>456085945</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>0.33%→0.47%</t>
+          <t>0.00%→0.10%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>56→81</t>
+          <t>0→25</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -1119,23 +1119,23 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>씨메스로보틱스</t>
+          <t>지투지바이오  (편출)</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-300038684</v>
+        <v>-526943937</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.23%→0.15%</t>
+          <t>0.12%→0.00%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>53→37</t>
+          <t>16→0</t>
         </is>
       </c>
     </row>
@@ -1163,23 +1163,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오  (편출)</t>
+          <t>씨메스로보틱스</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-526943937</v>
+        <v>-300038684</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.12%→0.00%</t>
+          <t>0.23%→0.15%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>16→0</t>
+          <t>53→37</t>
         </is>
       </c>
     </row>
